--- a/MarineBoard/production/MarineBoard-positions.xlsx
+++ b/MarineBoard/production/MarineBoard-positions.xlsx
@@ -27,20 +27,14 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002F5597"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -57,9 +51,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G154"/>
+  <dimension ref="A1:G155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1562,24 +1554,24 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1A</t>
+          <t>22uH</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>FUSE-TH_XF-506P</t>
+          <t>IND-SMD_L12.5-W12.5_B82477P4XX</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>229.1</v>
+        <v>234.5</v>
       </c>
       <c r="E37" t="n">
-        <v>-77.875</v>
+        <v>-87.375</v>
       </c>
       <c r="F37" t="n">
         <v>180</v>
@@ -1593,27 +1585,27 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>22uH</t>
+          <t>BLM21PG121SN1D</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>IND-SMD_L12.5-W12.5_B82477P4XX</t>
+          <t>L_0805_2012Metric</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>234.5</v>
+        <v>220</v>
       </c>
       <c r="E38" t="n">
-        <v>-87.375</v>
+        <v>-94.6875</v>
       </c>
       <c r="F38" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1624,7 +1616,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1638,13 +1630,13 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>220</v>
+        <v>218.25</v>
       </c>
       <c r="E39" t="n">
         <v>-94.6875</v>
       </c>
       <c r="F39" t="n">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1655,12 +1647,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>L4</t>
+          <t>L7</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BLM21PG121SN1D</t>
+          <t>FerriteBead</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1669,13 +1661,13 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>218.25</v>
+        <v>232.9375</v>
       </c>
       <c r="E40" t="n">
-        <v>-94.6875</v>
+        <v>-46.75</v>
       </c>
       <c r="F40" t="n">
-        <v>-90</v>
+        <v>180</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1686,27 +1678,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>L7</t>
+          <t>L8</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>FerriteBead</t>
+          <t>DLW21SN900SQ2L</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>L_0805_2012Metric</t>
+          <t>FILTER-SMD_4P-L2.0-W1.2-BL_DLW21H</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>232.9375</v>
+        <v>268.08</v>
       </c>
       <c r="E41" t="n">
-        <v>-46.75</v>
+        <v>-51.15</v>
       </c>
       <c r="F41" t="n">
-        <v>180</v>
+        <v>-90</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1717,27 +1709,27 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>L8</t>
+          <t>L9</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DLW21SN900SQ2L</t>
+          <t>FerriteBead</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>FILTER-SMD_4P-L2.0-W1.2-BL_DLW21H</t>
+          <t>L_0805_2012Metric</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>268.08</v>
+        <v>265.75</v>
       </c>
       <c r="E42" t="n">
-        <v>-51.15</v>
+        <v>-69.77</v>
       </c>
       <c r="F42" t="n">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1748,7 +1740,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>L9</t>
+          <t>L10</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1762,13 +1754,13 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>265.75</v>
+        <v>266.5</v>
       </c>
       <c r="E43" t="n">
-        <v>-69.77</v>
+        <v>-75.3725</v>
       </c>
       <c r="F43" t="n">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1779,27 +1771,27 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>L10</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>FerriteBead</t>
+          <t>S8050</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>L_0805_2012Metric</t>
+          <t>SOT-23</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>266.5</v>
+        <v>208.8825</v>
       </c>
       <c r="E44" t="n">
-        <v>-75.3725</v>
+        <v>-85.05</v>
       </c>
       <c r="F44" t="n">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1810,7 +1802,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1824,13 +1816,13 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>208.8825</v>
+        <v>257.5</v>
       </c>
       <c r="E45" t="n">
-        <v>-85.05</v>
+        <v>-70</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1841,27 +1833,27 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>S8050</t>
+          <t>5.1K</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SOT-23</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>257.5</v>
+        <v>200.515</v>
       </c>
       <c r="E46" t="n">
-        <v>-70</v>
+        <v>-49.9</v>
       </c>
       <c r="F46" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1872,7 +1864,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1886,10 +1878,10 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>200.515</v>
+        <v>200.545</v>
       </c>
       <c r="E47" t="n">
-        <v>-49.9</v>
+        <v>-51.65</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -1903,12 +1895,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5.1K</t>
+          <t>33R</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1917,10 +1909,10 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>200.545</v>
+        <v>205.015</v>
       </c>
       <c r="E48" t="n">
-        <v>-51.65</v>
+        <v>-50.15</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -1934,7 +1926,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R6</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1951,7 +1943,7 @@
         <v>205.015</v>
       </c>
       <c r="E49" t="n">
-        <v>-50.15</v>
+        <v>-51.65</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -1965,27 +1957,27 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>R6</t>
+          <t>R7</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>33R</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>R_0805_2012Metric</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>205.015</v>
+        <v>270.5875</v>
       </c>
       <c r="E50" t="n">
-        <v>-51.65</v>
+        <v>-58.8</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -1996,7 +1988,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>R7</t>
+          <t>R9</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2013,10 +2005,10 @@
         <v>270.5875</v>
       </c>
       <c r="E51" t="n">
-        <v>-58.8</v>
+        <v>-62.77</v>
       </c>
       <c r="F51" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2027,27 +2019,27 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R11</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>200m</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>R_0805_2012Metric</t>
+          <t>R_0201_0603Metric</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>270.5875</v>
+        <v>226.905</v>
       </c>
       <c r="E52" t="n">
-        <v>-62.77</v>
+        <v>-83.125</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2058,27 +2050,27 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>R11</t>
+          <t>R15</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>200m</t>
+          <t>10K</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>R_0201_0603Metric</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>226.905</v>
+        <v>200.575</v>
       </c>
       <c r="E53" t="n">
-        <v>-83.125</v>
+        <v>-59.49</v>
       </c>
       <c r="F53" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2089,24 +2081,24 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>R15</t>
+          <t>R19</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>120</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>R_0805_2012Metric</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>200.575</v>
+        <v>260.2</v>
       </c>
       <c r="E54" t="n">
-        <v>-59.49</v>
+        <v>-57.0375</v>
       </c>
       <c r="F54" t="n">
         <v>90</v>
@@ -2120,27 +2112,27 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>R19</t>
+          <t>R20</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>10K</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>R_0805_2012Metric</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>260.2</v>
+        <v>260.44</v>
       </c>
       <c r="E55" t="n">
-        <v>-57.0375</v>
+        <v>-62.2</v>
       </c>
       <c r="F55" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2151,27 +2143,27 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>R20</t>
+          <t>R24</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>120</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>R_0805_2012Metric</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>260.44</v>
+        <v>258.2</v>
       </c>
       <c r="E56" t="n">
-        <v>-62.2</v>
+        <v>-57.0375</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2182,27 +2174,27 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>R24</t>
+          <t>R25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>10K</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>R_0805_2012Metric</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>258.2</v>
+        <v>258.19</v>
       </c>
       <c r="E57" t="n">
-        <v>-57.0375</v>
+        <v>-63.7</v>
       </c>
       <c r="F57" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2213,7 +2205,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>R25</t>
+          <t>R27</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2227,13 +2219,13 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>258.19</v>
+        <v>238.5</v>
       </c>
       <c r="E58" t="n">
-        <v>-63.7</v>
+        <v>-67.73999999999999</v>
       </c>
       <c r="F58" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2244,7 +2236,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>R27</t>
+          <t>R28</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2258,10 +2250,10 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>238.5</v>
+        <v>246.5</v>
       </c>
       <c r="E59" t="n">
-        <v>-67.73999999999999</v>
+        <v>-67.8</v>
       </c>
       <c r="F59" t="n">
         <v>90</v>
@@ -2275,12 +2267,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>R28</t>
+          <t>R30</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>1K</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2289,13 +2281,13 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>246.5</v>
+        <v>201.32</v>
       </c>
       <c r="E60" t="n">
-        <v>-67.8</v>
+        <v>-87.04000000000001</v>
       </c>
       <c r="F60" t="n">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2306,27 +2298,27 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>R30</t>
+          <t>R35</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1K</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>R_0805_2012Metric</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>201.32</v>
+        <v>270.8375</v>
       </c>
       <c r="E61" t="n">
-        <v>-87.04000000000001</v>
+        <v>-67.02</v>
       </c>
       <c r="F61" t="n">
-        <v>-90</v>
+        <v>180</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2337,7 +2329,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>R35</t>
+          <t>R36</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2354,7 +2346,7 @@
         <v>270.8375</v>
       </c>
       <c r="E62" t="n">
-        <v>-67.02</v>
+        <v>-78.27</v>
       </c>
       <c r="F62" t="n">
         <v>180</v>
@@ -2368,12 +2360,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>R36</t>
+          <t>R38</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2382,13 +2374,13 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>270.8375</v>
+        <v>267.3375</v>
       </c>
       <c r="E63" t="n">
-        <v>-78.27</v>
+        <v>-67.02</v>
       </c>
       <c r="F63" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2399,7 +2391,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>R38</t>
+          <t>R39</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2413,10 +2405,10 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>267.3375</v>
+        <v>267.1625</v>
       </c>
       <c r="E64" t="n">
-        <v>-67.02</v>
+        <v>-78.27</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -2430,27 +2422,27 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>R39</t>
+          <t>R41</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>1K</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>R_0805_2012Metric</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>267.1625</v>
+        <v>208.56</v>
       </c>
       <c r="E65" t="n">
-        <v>-78.27</v>
+        <v>-88.8</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -2461,12 +2453,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>R41</t>
+          <t>R42</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1K</t>
+          <t>10K</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2478,10 +2470,10 @@
         <v>208.56</v>
       </c>
       <c r="E66" t="n">
-        <v>-88.8</v>
+        <v>-87.8</v>
       </c>
       <c r="F66" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2492,7 +2484,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>R42</t>
+          <t>R43</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2506,13 +2498,13 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>208.56</v>
+        <v>257.9375</v>
       </c>
       <c r="E67" t="n">
-        <v>-87.8</v>
+        <v>-67.7</v>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2523,12 +2515,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>R43</t>
+          <t>R44</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>1K</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2540,7 +2532,7 @@
         <v>257.9375</v>
       </c>
       <c r="E68" t="n">
-        <v>-67.7</v>
+        <v>-66.7</v>
       </c>
       <c r="F68" t="n">
         <v>180</v>
@@ -2554,27 +2546,27 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>R44</t>
+          <t>R47</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1K</t>
+          <t>2K2</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>R_2512_6332Metric</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>257.9375</v>
+        <v>218.0375</v>
       </c>
       <c r="E69" t="n">
-        <v>-66.7</v>
+        <v>-68.25</v>
       </c>
       <c r="F69" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -2585,27 +2577,27 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>R47</t>
+          <t>R49</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2K2</t>
+          <t>120</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>R_2512_6332Metric</t>
+          <t>R_0805_2012Metric</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>218.0375</v>
+        <v>230.575</v>
       </c>
       <c r="E70" t="n">
-        <v>-68.25</v>
+        <v>-61.5</v>
       </c>
       <c r="F70" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -2616,27 +2608,27 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>R49</t>
+          <t>U14</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>PC817C-S</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>R_0805_2012Metric</t>
+          <t>SOP-4_L6.5-W4.6-P2.54-LS10.3-TL</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>230.575</v>
+        <v>207.325</v>
       </c>
       <c r="E71" t="n">
-        <v>-61.5</v>
+        <v>-66.5</v>
       </c>
       <c r="F71" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -2647,27 +2639,27 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U17</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SM10B-GHS-TB</t>
+          <t>PC817C-S</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CONN-SMD_SM10B-GHS-TB</t>
+          <t>SOP-4_L6.5-W4.6-P2.54-LS10.3-TL</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>244.62</v>
+        <v>204.55</v>
       </c>
       <c r="E72" t="n">
-        <v>-56.35</v>
+        <v>-88.75</v>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -2678,24 +2670,24 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>U14</t>
+          <t>U22</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PC817C-S</t>
+          <t>SN74LVC1G14DBVR</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>SOP-4_L6.5-W4.6-P2.54-LS10.3-TL</t>
+          <t>SOT-23-5</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>207.325</v>
+        <v>227.075</v>
       </c>
       <c r="E73" t="n">
-        <v>-66.5</v>
+        <v>-63</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -2709,89 +2701,89 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>U17</t>
+          <t>BUZZER1</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PC817C-S</t>
+          <t>KLJ-4020</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>SOP-4_L6.5-W4.6-P2.54-LS10.3-TL</t>
+          <t>BUZ-SMD_L4.0-W4.0-P3.50-L</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>204.55</v>
+        <v>257.6875</v>
       </c>
       <c r="E74" t="n">
-        <v>-88.75</v>
+        <v>-68.2</v>
       </c>
       <c r="F74" t="n">
-        <v>-90</v>
+        <v>180</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>U22</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SN74LVC1G14DBVR</t>
+          <t>0.1uF</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SOT-23-5</t>
+          <t>C_0402_1005Metric</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>227.075</v>
+        <v>218.25</v>
       </c>
       <c r="E75" t="n">
-        <v>-63</v>
+        <v>-46.02</v>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BUZZER1</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>KLJ-4020</t>
+          <t>22uF</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>BUZ-SMD_L4.0-W4.0-P3.50-L</t>
+          <t>C_0402_1005Metric</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>257.6875</v>
+        <v>213.23</v>
       </c>
       <c r="E76" t="n">
-        <v>-68.2</v>
+        <v>-46.5</v>
       </c>
       <c r="F76" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -2802,7 +2794,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2816,10 +2808,10 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>218.25</v>
+        <v>209</v>
       </c>
       <c r="E77" t="n">
-        <v>-46.02</v>
+        <v>-47.23</v>
       </c>
       <c r="F77" t="n">
         <v>90</v>
@@ -2833,12 +2825,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>22uF</t>
+          <t>6.8pF</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2847,13 +2839,13 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>213.23</v>
+        <v>208.27</v>
       </c>
       <c r="E78" t="n">
-        <v>-46.5</v>
+        <v>-49.75</v>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -2864,12 +2856,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C8</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0.1uF</t>
+          <t>22uF</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2878,13 +2870,13 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E79" t="n">
         <v>-47.23</v>
       </c>
       <c r="F79" t="n">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -2895,27 +2887,27 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C16</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>6.8pF</t>
+          <t>4.7uF</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>C_0402_1005Metric</t>
+          <t>C_1206_3216Metric</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>208.27</v>
+        <v>216</v>
       </c>
       <c r="E80" t="n">
-        <v>-49.75</v>
+        <v>-89.40000000000001</v>
       </c>
       <c r="F80" t="n">
-        <v>180</v>
+        <v>-90</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -2926,27 +2918,27 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>C8</t>
+          <t>C17</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>22uF</t>
+          <t>10uF</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>C_0402_1005Metric</t>
+          <t>C_1206_3216Metric</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>210</v>
+        <v>218.5</v>
       </c>
       <c r="E81" t="n">
-        <v>-47.23</v>
+        <v>-89.40000000000001</v>
       </c>
       <c r="F81" t="n">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -2957,27 +2949,27 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>C16</t>
+          <t>C18</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>4.7uF</t>
+          <t>10nF</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>C_1206_3216Metric</t>
+          <t>C_0402_1005Metric</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>216</v>
+        <v>228.2</v>
       </c>
       <c r="E82" t="n">
-        <v>-89.40000000000001</v>
+        <v>-95.895</v>
       </c>
       <c r="F82" t="n">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -2988,27 +2980,27 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>C17</t>
+          <t>C20</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>10uF</t>
+          <t>220uF 10V</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>C_1206_3216Metric</t>
+          <t>CAP-SMD_BD6.3-L6.6-W6.6-FD</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>218.5</v>
+        <v>232.42</v>
       </c>
       <c r="E83" t="n">
-        <v>-89.40000000000001</v>
+        <v>-80.875</v>
       </c>
       <c r="F83" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -3019,12 +3011,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>C18</t>
+          <t>C21</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>10nF</t>
+          <t>1.5nF</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3033,13 +3025,13 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>228.2</v>
+        <v>227.98</v>
       </c>
       <c r="E84" t="n">
-        <v>-95.895</v>
+        <v>-83.875</v>
       </c>
       <c r="F84" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -3050,27 +3042,27 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>C20</t>
+          <t>C22</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>220uF 10V</t>
+          <t>0.1uF</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>CAP-SMD_BD6.3-L6.6-W6.6-FD</t>
+          <t>C_0402_1005Metric</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>232.42</v>
+        <v>228.02</v>
       </c>
       <c r="E85" t="n">
-        <v>-80.875</v>
+        <v>-84.875</v>
       </c>
       <c r="F85" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -3081,12 +3073,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>C21</t>
+          <t>C23</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1.5nF</t>
+          <t>150pF</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3095,10 +3087,10 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>227.98</v>
+        <v>227</v>
       </c>
       <c r="E86" t="n">
-        <v>-83.875</v>
+        <v>-86.125</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -3112,7 +3104,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>C22</t>
+          <t>C24</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3126,13 +3118,13 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>228.02</v>
+        <v>234</v>
       </c>
       <c r="E87" t="n">
-        <v>-84.875</v>
+        <v>-46.02</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -3143,12 +3135,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>C23</t>
+          <t>C25</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>150pF</t>
+          <t>10uF</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3157,13 +3149,13 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="E88" t="n">
-        <v>-86.125</v>
+        <v>-46.02</v>
       </c>
       <c r="F88" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -3174,12 +3166,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>C24</t>
+          <t>C33</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0.1uF</t>
+          <t>4.7uF</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3188,13 +3180,13 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>234</v>
+        <v>254.8</v>
       </c>
       <c r="E89" t="n">
-        <v>-46.02</v>
+        <v>-85.27</v>
       </c>
       <c r="F89" t="n">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -3205,12 +3197,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>C25</t>
+          <t>C36</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>10uF</t>
+          <t>0.1uF</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3219,13 +3211,13 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>233</v>
+        <v>259.55</v>
       </c>
       <c r="E90" t="n">
-        <v>-46.02</v>
+        <v>-85.27</v>
       </c>
       <c r="F90" t="n">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -3236,12 +3228,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>C33</t>
+          <t>C40</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>4.7uF</t>
+          <t>0.1uF</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3250,10 +3242,10 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>254.8</v>
+        <v>254.65</v>
       </c>
       <c r="E91" t="n">
-        <v>-85.27</v>
+        <v>-70.79000000000001</v>
       </c>
       <c r="F91" t="n">
         <v>90</v>
@@ -3267,27 +3259,27 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>C36</t>
+          <t>CN1</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0.1uF</t>
+          <t>MKDSN 1,5/ 2-5,08</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>C_0402_1005Metric</t>
+          <t>CONN-TH_2P-P5.08_1729128</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>259.55</v>
+        <v>220.24</v>
       </c>
       <c r="E92" t="n">
-        <v>-85.27</v>
+        <v>-100.875</v>
       </c>
       <c r="F92" t="n">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -3298,7 +3290,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>CN1</t>
+          <t>CN2</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3312,10 +3304,10 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>220.24</v>
+        <v>246.8</v>
       </c>
       <c r="E93" t="n">
-        <v>-100.875</v>
+        <v>-100.75</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
@@ -3329,24 +3321,24 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CN2</t>
+          <t>CN3</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>MKDSN 1,5/ 2-5,08</t>
+          <t>SM04B-SRSS-TB (LF)(SN)</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>CONN-TH_2P-P5.08_1729128</t>
+          <t>CONN-SMD_4P-P1.00_SM04B-SRSS-TB-LF-SN</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>246.8</v>
+        <v>258.25</v>
       </c>
       <c r="E94" t="n">
-        <v>-100.75</v>
+        <v>-62.01</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
@@ -3360,24 +3352,24 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>CN3</t>
+          <t>CN4</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SM04B-SRSS-TB (LF)(SN)</t>
+          <t>BM10B-GHS-TBT</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>CONN-SMD_4P-P1.00_SM04B-SRSS-TB-LF-SN</t>
+          <t>CONN-SMD_BM10B-GHS-TBT-LF-SN</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>258.25</v>
+        <v>246.93</v>
       </c>
       <c r="E95" t="n">
-        <v>-62.01</v>
+        <v>-74.595</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
@@ -3453,24 +3445,24 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>LMBR340FT1G</t>
+          <t>WS2812B-2020</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>D_SOD-123F</t>
+          <t>LED_WS2812B-2020_PLCC4_2.0x2.0mm</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>223.85</v>
+        <v>252.275</v>
       </c>
       <c r="E98" t="n">
-        <v>-95.23999999999999</v>
+        <v>-70.67</v>
       </c>
       <c r="F98" t="n">
         <v>0</v>
@@ -3484,27 +3476,27 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>D8</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>VS-43CTQ100S-M3</t>
+          <t>LMBR340FT1G</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>D2PAK_L10.0-W9.0-P2.54-LS15.0-TL-1</t>
+          <t>D_SOD-123F</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>251.425</v>
+        <v>223.85</v>
       </c>
       <c r="E99" t="n">
-        <v>-90.75</v>
+        <v>-95.23999999999999</v>
       </c>
       <c r="F99" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -3515,27 +3507,27 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>D10</t>
+          <t>D8</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>PESD1CAN</t>
+          <t>VS-43CTQ100S-M3</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>SOT-23</t>
+          <t>D2PAK_L10.0-W9.0-P2.54-LS15.0-TL-1</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>267.8</v>
+        <v>251.425</v>
       </c>
       <c r="E100" t="n">
-        <v>-47.8125</v>
+        <v>-90.75</v>
       </c>
       <c r="F100" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -3546,27 +3538,27 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>D10</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ESD5Z3.3T1G</t>
+          <t>PESD1CAN</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>D_SOD-523</t>
+          <t>SOT-23</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>202.525</v>
+        <v>267.8</v>
       </c>
       <c r="E101" t="n">
-        <v>-67.23</v>
+        <v>-47.8125</v>
       </c>
       <c r="F101" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -3577,24 +3569,24 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>LED</t>
+          <t>ESD5Z3.3T1G</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>LED_0603_1608Metric</t>
+          <t>D_SOD-523</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>252.7875</v>
+        <v>202.525</v>
       </c>
       <c r="E102" t="n">
-        <v>-67</v>
+        <v>-67.23</v>
       </c>
       <c r="F102" t="n">
         <v>0</v>
@@ -3608,7 +3600,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>D17</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3622,13 +3614,13 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>252.825</v>
+        <v>252.7875</v>
       </c>
       <c r="E103" t="n">
-        <v>-69.5</v>
+        <v>-67</v>
       </c>
       <c r="F103" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -3701,12 +3693,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>10A</t>
+          <t>1A</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3715,13 +3707,13 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>259.85</v>
+        <v>229.07</v>
       </c>
       <c r="E106" t="n">
-        <v>-101</v>
+        <v>-75.17</v>
       </c>
       <c r="F106" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -3732,7 +3724,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F3</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3746,13 +3738,13 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>205.95</v>
+        <v>259.85</v>
       </c>
       <c r="E107" t="n">
-        <v>-75.5</v>
+        <v>-101</v>
       </c>
       <c r="F107" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -3763,24 +3755,24 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Flash1</t>
+          <t>F4</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Flash</t>
+          <t>10A</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>SW_Push_1P1T_XKB_TS-1187A</t>
+          <t>FUSE-TH_XF-506P</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>246.5</v>
+        <v>205.95</v>
       </c>
       <c r="E108" t="n">
-        <v>-69.25</v>
+        <v>-75.5</v>
       </c>
       <c r="F108" t="n">
         <v>180</v>
@@ -3794,27 +3786,27 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>J1</t>
+          <t>Flash1</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>USB_C_Receptacle_USB2.0_16P</t>
+          <t>Flash</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>USB_C_Receptacle_HCTL_HC-TYPE-C-16P-01A</t>
+          <t>SW_Push_1P1T_XKB_TS-1187A</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>198.755</v>
+        <v>246.5</v>
       </c>
       <c r="E109" t="n">
-        <v>-50.9</v>
+        <v>-69.11499999999999</v>
       </c>
       <c r="F109" t="n">
-        <v>-90</v>
+        <v>180</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -3825,27 +3817,27 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>JP1</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>CAN Bus Term</t>
+          <t>USB_C_Receptacle_USB2.0_16P</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>PinHeader_1x02_P1.27mm_Vertical</t>
+          <t>USB_C_Receptacle_HCTL_HC-TYPE-C-16P-01A</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>268</v>
+        <v>198.755</v>
       </c>
       <c r="E110" t="n">
-        <v>-55</v>
+        <v>-50.9</v>
       </c>
       <c r="F110" t="n">
-        <v>180</v>
+        <v>-90</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -3856,27 +3848,27 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>JP1</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>1uH 3.3A 40mΩ</t>
+          <t>CAN Bus Term</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>L_1008_2520Metric</t>
+          <t>PinHeader_1x02_P1.27mm_Vertical</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>216.825</v>
+        <v>268</v>
       </c>
       <c r="E111" t="n">
-        <v>-48.5</v>
+        <v>-55</v>
       </c>
       <c r="F111" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -3887,27 +3879,27 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>L5</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>CDRH104RNP-150NC</t>
+          <t>1uH 3.3A 40mΩ</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>IND-SMD_L10.2-W10.0</t>
+          <t>L_1008_2520Metric</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>235.2</v>
+        <v>216.825</v>
       </c>
       <c r="E112" t="n">
-        <v>-92.37</v>
+        <v>-48.5</v>
       </c>
       <c r="F112" t="n">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -3918,27 +3910,27 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>L6</t>
+          <t>L5</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>BLM21PG121SN1D</t>
+          <t>CDRH104RNP-150NC</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>L_0805_2012Metric</t>
+          <t>IND-SMD_L10.2-W10.0</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>237.95</v>
+        <v>235.2</v>
       </c>
       <c r="E113" t="n">
-        <v>-78.9375</v>
+        <v>-92.37</v>
       </c>
       <c r="F113" t="n">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -3949,24 +3941,24 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>L6</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>BUK762R4-60E</t>
+          <t>BLM21PG121SN1D</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>TO-263-2_L10.1-W9.1-P5.08-LS15.2-BR</t>
+          <t>L_0805_2012Metric</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>264.75</v>
+        <v>237.85</v>
       </c>
       <c r="E114" t="n">
-        <v>-88.43000000000001</v>
+        <v>-78.9375</v>
       </c>
       <c r="F114" t="n">
         <v>90</v>
@@ -3980,27 +3972,27 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>BUK762R4-60E</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>TO-263-2_L10.1-W9.1-P5.08-LS15.2-BR</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>215.76</v>
+        <v>264.75</v>
       </c>
       <c r="E115" t="n">
-        <v>-50.5</v>
+        <v>-88.43000000000001</v>
       </c>
       <c r="F115" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -4011,24 +4003,24 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>100K</t>
+          <t>10K</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>R_0805_2012Metric</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>208.1625</v>
+        <v>215.76</v>
       </c>
       <c r="E116" t="n">
-        <v>-51.75</v>
+        <v>-50.5</v>
       </c>
       <c r="F116" t="n">
         <v>180</v>
@@ -4042,12 +4034,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>R8</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>22K</t>
+          <t>100K</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4056,7 +4048,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>211.6625</v>
+        <v>208.1625</v>
       </c>
       <c r="E117" t="n">
         <v>-51.75</v>
@@ -4073,27 +4065,27 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>R10</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>22K</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>R_0805_2012Metric</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>229.01</v>
+        <v>211.6625</v>
       </c>
       <c r="E118" t="n">
-        <v>-87.375</v>
+        <v>-51.75</v>
       </c>
       <c r="F118" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -4104,12 +4096,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R10</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>3k24</t>
+          <t>10K</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4118,7 +4110,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>227.01</v>
+        <v>229.01</v>
       </c>
       <c r="E119" t="n">
         <v>-87.375</v>
@@ -4135,27 +4127,27 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>R13</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>3k24</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>R_0603_1608Metric</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>229.575</v>
+        <v>227.01</v>
       </c>
       <c r="E120" t="n">
-        <v>-86.125</v>
+        <v>-87.375</v>
       </c>
       <c r="F120" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -4166,27 +4158,27 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>R14</t>
+          <t>R13</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>549</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>R_0805_2012Metric</t>
+          <t>R_0603_1608Metric</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>202.9875</v>
+        <v>229.575</v>
       </c>
       <c r="E121" t="n">
-        <v>-59</v>
+        <v>-86.125</v>
       </c>
       <c r="F121" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -4197,27 +4189,27 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>R16</t>
+          <t>R14</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>10K/1W</t>
+          <t>120</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>R_2512_6332Metric</t>
+          <t>R_0805_2012Metric</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>205.325</v>
+        <v>202.9875</v>
       </c>
       <c r="E122" t="n">
-        <v>-62</v>
+        <v>-59</v>
       </c>
       <c r="F122" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -4228,24 +4220,24 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>R21</t>
+          <t>R16</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>10K/1W</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>R_0805_2012Metric</t>
+          <t>R_2512_6332Metric</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>263.9125</v>
+        <v>205.325</v>
       </c>
       <c r="E123" t="n">
-        <v>-47.75</v>
+        <v>-62</v>
       </c>
       <c r="F123" t="n">
         <v>180</v>
@@ -4259,27 +4251,27 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>R22</t>
+          <t>R21</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>1K</t>
+          <t>120</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>R_0805_2012Metric</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>202.335</v>
+        <v>263.9125</v>
       </c>
       <c r="E124" t="n">
-        <v>-65.98</v>
+        <v>-47.75</v>
       </c>
       <c r="F124" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -4290,27 +4282,27 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>R23</t>
+          <t>R22</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>1K</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>R_0805_2012Metric</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>207.9125</v>
+        <v>202.335</v>
       </c>
       <c r="E125" t="n">
-        <v>-67.48</v>
+        <v>-65.98</v>
       </c>
       <c r="F125" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -4321,24 +4313,24 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>R26</t>
+          <t>R23</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>120</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>R_0805_2012Metric</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>208.835</v>
+        <v>207.9125</v>
       </c>
       <c r="E126" t="n">
-        <v>-64.98</v>
+        <v>-67.48</v>
       </c>
       <c r="F126" t="n">
         <v>180</v>
@@ -4352,12 +4344,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>R29</t>
+          <t>R26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>1K</t>
+          <t>10K</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4366,13 +4358,13 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>248.715</v>
+        <v>208.835</v>
       </c>
       <c r="E127" t="n">
-        <v>-78</v>
+        <v>-64.98</v>
       </c>
       <c r="F127" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -4383,27 +4375,27 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>R31</t>
+          <t>R29</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1K</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>R_0805_2012Metric</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>257.1375</v>
+        <v>248.715</v>
       </c>
       <c r="E128" t="n">
-        <v>-85.25</v>
+        <v>-78.09</v>
       </c>
       <c r="F128" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -4414,24 +4406,24 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>R32</t>
+          <t>R31</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>R_0805_2012Metric</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>248.715</v>
+        <v>257.1375</v>
       </c>
       <c r="E129" t="n">
-        <v>-79</v>
+        <v>-85.25</v>
       </c>
       <c r="F129" t="n">
         <v>180</v>
@@ -4445,12 +4437,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>R33</t>
+          <t>R32</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>470R</t>
+          <t>10K</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4459,13 +4451,13 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>251.565</v>
+        <v>248.715</v>
       </c>
       <c r="E130" t="n">
-        <v>-68.25</v>
+        <v>-79.09</v>
       </c>
       <c r="F130" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -4476,7 +4468,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>R34</t>
+          <t>R33</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -4490,13 +4482,13 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>253.585</v>
+        <v>251.58</v>
       </c>
       <c r="E131" t="n">
-        <v>-68.25</v>
+        <v>-68.37</v>
       </c>
       <c r="F131" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
@@ -4507,27 +4499,27 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>R40</t>
+          <t>R34</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>R0402</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>264.74</v>
+        <v>253.7</v>
       </c>
       <c r="E132" t="n">
-        <v>-81.75</v>
+        <v>-68.41</v>
       </c>
       <c r="F132" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -4538,24 +4530,24 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>R46</t>
+          <t>R40</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>47K/1W</t>
+          <t>10K</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>R_2512_6332Metric</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>213.7875</v>
+        <v>264.74</v>
       </c>
       <c r="E133" t="n">
-        <v>-60.25</v>
+        <v>-81.75</v>
       </c>
       <c r="F133" t="n">
         <v>180</v>
@@ -4569,27 +4561,27 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>R48</t>
+          <t>R46</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>47K</t>
+          <t>47K/1W</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>R_2512_6332Metric</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>230.075</v>
+        <v>213.7875</v>
       </c>
       <c r="E134" t="n">
-        <v>-58.5</v>
+        <v>-60.25</v>
       </c>
       <c r="F134" t="n">
-        <v>-90</v>
+        <v>180</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -4600,27 +4592,27 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>R50</t>
+          <t>R48</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>47K</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>R_0805_2012Metric</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>251.6375</v>
+        <v>230.075</v>
       </c>
       <c r="E135" t="n">
-        <v>-78.5</v>
+        <v>-58.5</v>
       </c>
       <c r="F135" t="n">
-        <v>180</v>
+        <v>-90</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -4631,27 +4623,27 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Relay1</t>
+          <t>R50</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>SRD-12VDC-SL-C</t>
+          <t>120</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>RELAY-TH_SRD-XXVDC-XL-C</t>
+          <t>R_0805_2012Metric</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>214.3</v>
+        <v>251.6375</v>
       </c>
       <c r="E136" t="n">
-        <v>-81.5</v>
+        <v>-78.59</v>
       </c>
       <c r="F136" t="n">
-        <v>-90</v>
+        <v>180</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -4662,27 +4654,27 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Reset1</t>
+          <t>Relay1</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Reset</t>
+          <t>SRD-12VDC-SL-C</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>SW_Push_1P1T_XKB_TS-1187A</t>
+          <t>RELAY-TH_SRD-XXVDC-XL-C</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>238.365819</v>
+        <v>214.3</v>
       </c>
       <c r="E137" t="n">
-        <v>-69.159688</v>
+        <v>-81.5</v>
       </c>
       <c r="F137" t="n">
-        <v>180</v>
+        <v>-90</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -4693,24 +4685,24 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>U1</t>
+          <t>Reset1</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>SY8089A1AAC</t>
+          <t>Reset</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>TSOT-23-5</t>
+          <t>SW_Push_1P1T_XKB_TS-1187A</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>212.6375</v>
+        <v>238.36</v>
       </c>
       <c r="E138" t="n">
-        <v>-48.8</v>
+        <v>-69.11499999999999</v>
       </c>
       <c r="F138" t="n">
         <v>180</v>
@@ -4724,27 +4716,27 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>U2</t>
+          <t>U1</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>INA226</t>
+          <t>SY8089A1AAC</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>VSSOP-10_3x3mm_P0.5mm</t>
+          <t>TSOT-23-5</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>265.55</v>
+        <v>212.6375</v>
       </c>
       <c r="E139" t="n">
-        <v>-61.29</v>
+        <v>-48.8</v>
       </c>
       <c r="F139" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -4755,27 +4747,27 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>U3</t>
+          <t>U2</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>TPS5430DDA</t>
+          <t>INA226</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>TI_SO-PowerPAD-8_ThermalVias</t>
+          <t>VSSOP-10_3x3mm_P0.5mm</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>225.25</v>
+        <v>265.55</v>
       </c>
       <c r="E140" t="n">
-        <v>-90.875</v>
+        <v>-61.29</v>
       </c>
       <c r="F140" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -4786,27 +4778,27 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>U4</t>
+          <t>U3</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>DB125-3.5-2P-GN-S</t>
+          <t>TPS5430DDA</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>CONN-TH_2P-P3.50_L7.4-W7.0</t>
+          <t>TI_SO-PowerPAD-8_ThermalVias</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>273.75</v>
+        <v>225.25</v>
       </c>
       <c r="E141" t="n">
-        <v>-60.77</v>
+        <v>-90.875</v>
       </c>
       <c r="F141" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -4817,7 +4809,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>U5</t>
+          <t>U4</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4831,10 +4823,10 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>274</v>
+        <v>273.75</v>
       </c>
       <c r="E142" t="n">
-        <v>-68.77</v>
+        <v>-60.77</v>
       </c>
       <c r="F142" t="n">
         <v>90</v>
@@ -4848,7 +4840,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>U6</t>
+          <t>U5</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4865,7 +4857,7 @@
         <v>274</v>
       </c>
       <c r="E143" t="n">
-        <v>-76.27</v>
+        <v>-68.77</v>
       </c>
       <c r="F143" t="n">
         <v>90</v>
@@ -4879,27 +4871,27 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>U7</t>
+          <t>U6</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>DB125-3.5-3P-GN-S</t>
+          <t>DB125-3.5-2P-GN-S</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>CONN-TH_3P-P3.50_L7.4-W10.5</t>
+          <t>CONN-TH_2P-P3.50_L7.4-W7.0</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>273.25</v>
+        <v>274</v>
       </c>
       <c r="E144" t="n">
-        <v>-51.25</v>
+        <v>-76.27</v>
       </c>
       <c r="F144" t="n">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -4910,27 +4902,27 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U7</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>ESP32-S3-WROOM-2-N32R16V</t>
+          <t>DB125-3.5-3P-GN-S</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>ESP32-S3-WROOM-2</t>
+          <t>CONN-TH_3P-P3.50_L7.4-W10.5</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>244.61</v>
+        <v>273.25</v>
       </c>
       <c r="E145" t="n">
-        <v>-50.91</v>
+        <v>-51.25</v>
       </c>
       <c r="F145" t="n">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -4941,24 +4933,24 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>DB125-3.5-3P-GN-S</t>
+          <t>ESP32-S3-WROOM-2-N32R16V</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>CONN-TH_3P-P3.50_L7.4-W10.5</t>
+          <t>ESP32-S3-WROOM-2</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>206.5</v>
+        <v>244.61</v>
       </c>
       <c r="E146" t="n">
-        <v>-41.25</v>
+        <v>-50.91</v>
       </c>
       <c r="F146" t="n">
         <v>0</v>
@@ -4972,24 +4964,24 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U9</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>SN65HVD230DR</t>
+          <t>DB125-3.5-3P-GN-S</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>SOIC-8_3.9x4.9mm_P1.27mm</t>
+          <t>CONN-TH_3P-P3.50_L7.4-W10.5</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>262.275</v>
+        <v>206.5</v>
       </c>
       <c r="E147" t="n">
-        <v>-51.825</v>
+        <v>-41.25</v>
       </c>
       <c r="F147" t="n">
         <v>0</v>
@@ -5003,27 +4995,27 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>DB125-3.5-3P-GN-S</t>
+          <t>SN65HVD230DR</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>CONN-TH_3P-P3.50_L7.4-W10.5</t>
+          <t>SOIC-8_3.9x4.9mm_P1.27mm</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>206.55</v>
+        <v>262.275</v>
       </c>
       <c r="E148" t="n">
-        <v>-101.6</v>
+        <v>-51.825</v>
       </c>
       <c r="F148" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -5034,7 +5026,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>U13</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -5048,13 +5040,13 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>197.325</v>
+        <v>206.55</v>
       </c>
       <c r="E149" t="n">
-        <v>-63.25</v>
+        <v>-101.6</v>
       </c>
       <c r="F149" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -5065,27 +5057,27 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>U13</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>PC817C-S</t>
+          <t>DB125-3.5-3P-GN-S</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>SOP-4_L6.5-W4.6-P2.54-LS10.3-TL</t>
+          <t>CONN-TH_3P-P3.50_L7.4-W10.5</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>247.8</v>
+        <v>197.325</v>
       </c>
       <c r="E150" t="n">
-        <v>-82.25</v>
+        <v>-63.25</v>
       </c>
       <c r="F150" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
@@ -5096,27 +5088,27 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>U18</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>INA226</t>
+          <t>PC817C-S</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>VSSOP-10_3x3mm_P0.5mm</t>
+          <t>SOP-4_L6.5-W4.6-P2.54-LS10.3-TL</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>266.3</v>
+        <v>247.8</v>
       </c>
       <c r="E151" t="n">
-        <v>-69.52</v>
+        <v>-82.25</v>
       </c>
       <c r="F151" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
@@ -5127,7 +5119,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>U19</t>
+          <t>U18</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -5141,10 +5133,10 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>267.25</v>
+        <v>266.3</v>
       </c>
       <c r="E152" t="n">
-        <v>-75.52</v>
+        <v>-69.52</v>
       </c>
       <c r="F152" t="n">
         <v>0</v>
@@ -5158,27 +5150,27 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>U21</t>
+          <t>U19</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>PC817C-S</t>
+          <t>INA226</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>SOP-4_L6.5-W4.6-P2.54-LS10.3-TL</t>
+          <t>VSSOP-10_3x3mm_P0.5mm</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>227.075</v>
+        <v>267.25</v>
       </c>
       <c r="E153" t="n">
-        <v>-62.75</v>
+        <v>-75.52</v>
       </c>
       <c r="F153" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
@@ -5189,29 +5181,60 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
+          <t>U21</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>PC817C-S</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>SOP-4_L6.5-W4.6-P2.54-LS10.3-TL</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>227.075</v>
+      </c>
+      <c r="E154" t="n">
+        <v>-62.75</v>
+      </c>
+      <c r="F154" t="n">
+        <v>90</v>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
           <t>U23</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
+      <c r="B155" t="inlineStr">
         <is>
           <t>MCP1407-E/MF_C640313</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr">
+      <c r="C155" t="inlineStr">
         <is>
           <t>DFN-8_L6.0-W5.0-P1.27-BL-EP4.0</t>
         </is>
       </c>
-      <c r="D154" t="n">
+      <c r="D155" t="n">
         <v>257.865</v>
       </c>
-      <c r="E154" t="n">
+      <c r="E155" t="n">
         <v>-80.3075</v>
       </c>
-      <c r="F154" t="n">
+      <c r="F155" t="n">
         <v>0</v>
       </c>
-      <c r="G154" t="inlineStr">
+      <c r="G155" t="inlineStr">
         <is>
           <t>Top</t>
         </is>

--- a/MarineBoard/production/MarineBoard-positions.xlsx
+++ b/MarineBoard/production/MarineBoard-positions.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G155"/>
+  <dimension ref="A1:G151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3011,12 +3011,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>C21</t>
+          <t>C24</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1.5nF</t>
+          <t>0.1uF</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3025,13 +3025,13 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>227.98</v>
+        <v>234</v>
       </c>
       <c r="E84" t="n">
-        <v>-83.875</v>
+        <v>-46.02</v>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -3042,12 +3042,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>C22</t>
+          <t>C25</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0.1uF</t>
+          <t>10uF</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3056,13 +3056,13 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>228.02</v>
+        <v>233</v>
       </c>
       <c r="E85" t="n">
-        <v>-84.875</v>
+        <v>-46.02</v>
       </c>
       <c r="F85" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -3073,12 +3073,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>C23</t>
+          <t>C33</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>150pF</t>
+          <t>1uF</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3087,13 +3087,13 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>227</v>
+        <v>254.8</v>
       </c>
       <c r="E86" t="n">
-        <v>-86.125</v>
+        <v>-85.27</v>
       </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>C24</t>
+          <t>C36</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3118,10 +3118,10 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>234</v>
+        <v>259.55</v>
       </c>
       <c r="E87" t="n">
-        <v>-46.02</v>
+        <v>-85.27</v>
       </c>
       <c r="F87" t="n">
         <v>-90</v>
@@ -3135,12 +3135,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>C25</t>
+          <t>C40</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>10uF</t>
+          <t>0.1uF</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3149,10 +3149,10 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>233</v>
+        <v>254.65</v>
       </c>
       <c r="E88" t="n">
-        <v>-46.02</v>
+        <v>-70.79000000000001</v>
       </c>
       <c r="F88" t="n">
         <v>90</v>
@@ -3166,27 +3166,27 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>C33</t>
+          <t>CN1</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>4.7uF</t>
+          <t>MKDSN 1,5/ 2-5,08</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>C_0402_1005Metric</t>
+          <t>CONN-TH_2P-P5.08_1729128</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>254.8</v>
+        <v>220.24</v>
       </c>
       <c r="E89" t="n">
-        <v>-85.27</v>
+        <v>-100.875</v>
       </c>
       <c r="F89" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -3197,27 +3197,27 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>C36</t>
+          <t>CN2</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0.1uF</t>
+          <t>MKDSN 1,5/ 2-5,08</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>C_0402_1005Metric</t>
+          <t>CONN-TH_2P-P5.08_1729128</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>259.55</v>
+        <v>246.8</v>
       </c>
       <c r="E90" t="n">
-        <v>-85.27</v>
+        <v>-100.75</v>
       </c>
       <c r="F90" t="n">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -3228,27 +3228,27 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>C40</t>
+          <t>CN3</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0.1uF</t>
+          <t>SM04B-SRSS-TB (LF)(SN)</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>C_0402_1005Metric</t>
+          <t>CONN-SMD_4P-P1.00_SM04B-SRSS-TB-LF-SN</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>254.65</v>
+        <v>258.25</v>
       </c>
       <c r="E91" t="n">
-        <v>-70.79000000000001</v>
+        <v>-62.01</v>
       </c>
       <c r="F91" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -3259,24 +3259,24 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CN1</t>
+          <t>CN4</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MKDSN 1,5/ 2-5,08</t>
+          <t>BM10B-GHS-TBT</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>CONN-TH_2P-P5.08_1729128</t>
+          <t>CONN-SMD_BM10B-GHS-TBT-LF-SN</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>220.24</v>
+        <v>246.93</v>
       </c>
       <c r="E92" t="n">
-        <v>-100.875</v>
+        <v>-74.595</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -3290,27 +3290,27 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>CN2</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>MKDSN 1,5/ 2-5,08</t>
+          <t>SS14</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>CONN-TH_2P-P5.08_1729128</t>
+          <t>D_SMA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>246.8</v>
+        <v>210.5</v>
       </c>
       <c r="E93" t="n">
-        <v>-100.75</v>
+        <v>-54.75</v>
       </c>
       <c r="F93" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -3321,27 +3321,27 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CN3</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SM04B-SRSS-TB (LF)(SN)</t>
+          <t>SS14</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>CONN-SMD_4P-P1.00_SM04B-SRSS-TB-LF-SN</t>
+          <t>D_SMA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>258.25</v>
+        <v>223</v>
       </c>
       <c r="E94" t="n">
-        <v>-62.01</v>
+        <v>-84.375</v>
       </c>
       <c r="F94" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -3352,24 +3352,24 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>CN4</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>BM10B-GHS-TBT</t>
+          <t>WS2812B-2020</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>CONN-SMD_BM10B-GHS-TBT-LF-SN</t>
+          <t>LED_WS2812B-2020_PLCC4_2.0x2.0mm</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>246.93</v>
+        <v>252.275</v>
       </c>
       <c r="E95" t="n">
-        <v>-74.595</v>
+        <v>-70.67</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
@@ -3383,27 +3383,27 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SS14</t>
+          <t>LMBR340FT1G</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>D_SMA</t>
+          <t>D_SOD-123F</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>210.5</v>
+        <v>223.85</v>
       </c>
       <c r="E96" t="n">
-        <v>-54.75</v>
+        <v>-95.23999999999999</v>
       </c>
       <c r="F96" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -3414,27 +3414,27 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D8</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SS14</t>
+          <t>VS-43CTQ100S-M3</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>D_SMA</t>
+          <t>D2PAK_L10.0-W9.0-P2.54-LS15.0-TL-1</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>223</v>
+        <v>251.425</v>
       </c>
       <c r="E97" t="n">
-        <v>-84.375</v>
+        <v>-90.75</v>
       </c>
       <c r="F97" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -3445,27 +3445,27 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D10</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>WS2812B-2020</t>
+          <t>PESD1CAN</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>LED_WS2812B-2020_PLCC4_2.0x2.0mm</t>
+          <t>SOT-23</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>252.275</v>
+        <v>267.8</v>
       </c>
       <c r="E98" t="n">
-        <v>-70.67</v>
+        <v>-47.8125</v>
       </c>
       <c r="F98" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -3476,24 +3476,24 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>LMBR340FT1G</t>
+          <t>ESD5Z3.3T1G</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>D_SOD-123F</t>
+          <t>D_SOD-523</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>223.85</v>
+        <v>202.525</v>
       </c>
       <c r="E99" t="n">
-        <v>-95.23999999999999</v>
+        <v>-67.23</v>
       </c>
       <c r="F99" t="n">
         <v>0</v>
@@ -3507,27 +3507,27 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>D8</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>VS-43CTQ100S-M3</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>D2PAK_L10.0-W9.0-P2.54-LS15.0-TL-1</t>
+          <t>LED_0603_1608Metric</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>251.425</v>
+        <v>252.7875</v>
       </c>
       <c r="E100" t="n">
-        <v>-90.75</v>
+        <v>-67</v>
       </c>
       <c r="F100" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -3538,24 +3538,24 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>D10</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PESD1CAN</t>
+          <t>S3MB-13-F</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>SOT-23</t>
+          <t>D_SMB</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>267.8</v>
+        <v>221.825</v>
       </c>
       <c r="E101" t="n">
-        <v>-47.8125</v>
+        <v>-62</v>
       </c>
       <c r="F101" t="n">
         <v>90</v>
@@ -3569,24 +3569,24 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ESD5Z3.3T1G</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>D_SOD-523</t>
+          <t>FUSE-TH_XF-506P</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>202.525</v>
+        <v>233.25</v>
       </c>
       <c r="E102" t="n">
-        <v>-67.23</v>
+        <v>-100.875</v>
       </c>
       <c r="F102" t="n">
         <v>0</v>
@@ -3600,27 +3600,27 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>LED</t>
+          <t>1A</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>LED_0603_1608Metric</t>
+          <t>FUSE-TH_XF-506P</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>252.7875</v>
+        <v>229.07</v>
       </c>
       <c r="E103" t="n">
-        <v>-67</v>
+        <v>-75.17</v>
       </c>
       <c r="F103" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -3631,27 +3631,27 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>D22</t>
+          <t>F3</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>S3MB-13-F</t>
+          <t>10A</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>D_SMB</t>
+          <t>FUSE-TH_XF-506P</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>221.825</v>
+        <v>259.85</v>
       </c>
       <c r="E104" t="n">
-        <v>-62</v>
+        <v>-101</v>
       </c>
       <c r="F104" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -3662,12 +3662,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>F4</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2A</t>
+          <t>10A</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3676,13 +3676,13 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>233.25</v>
+        <v>205.95</v>
       </c>
       <c r="E105" t="n">
-        <v>-100.875</v>
+        <v>-75.5</v>
       </c>
       <c r="F105" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -3693,24 +3693,24 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>Flash1</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>1A</t>
+          <t>Flash</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>FUSE-TH_XF-506P</t>
+          <t>SW_Push_1P1T_XKB_TS-1187A</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>229.07</v>
+        <v>246.5</v>
       </c>
       <c r="E106" t="n">
-        <v>-75.17</v>
+        <v>-69.11499999999999</v>
       </c>
       <c r="F106" t="n">
         <v>180</v>
@@ -3724,27 +3724,27 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>10A</t>
+          <t>USB_C_Receptacle_USB2.0_16P</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>FUSE-TH_XF-506P</t>
+          <t>USB_C_Receptacle_HCTL_HC-TYPE-C-16P-01A</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>259.85</v>
+        <v>198.755</v>
       </c>
       <c r="E107" t="n">
-        <v>-101</v>
+        <v>-50.9</v>
       </c>
       <c r="F107" t="n">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -3755,24 +3755,24 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>JP1</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>10A</t>
+          <t>CAN Bus Term</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>FUSE-TH_XF-506P</t>
+          <t>PinHeader_1x02_P1.27mm_Vertical</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>205.95</v>
+        <v>268</v>
       </c>
       <c r="E108" t="n">
-        <v>-75.5</v>
+        <v>-55</v>
       </c>
       <c r="F108" t="n">
         <v>180</v>
@@ -3786,27 +3786,27 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Flash1</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Flash</t>
+          <t>1uH 3.3A 40mΩ</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>SW_Push_1P1T_XKB_TS-1187A</t>
+          <t>L_1008_2520Metric</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>246.5</v>
+        <v>216.825</v>
       </c>
       <c r="E109" t="n">
-        <v>-69.11499999999999</v>
+        <v>-48.5</v>
       </c>
       <c r="F109" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -3817,24 +3817,24 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>J1</t>
+          <t>L5</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>USB_C_Receptacle_USB2.0_16P</t>
+          <t>CDRH104RNP-150NC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>USB_C_Receptacle_HCTL_HC-TYPE-C-16P-01A</t>
+          <t>IND-SMD_L10.2-W10.0</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>198.755</v>
+        <v>235.2</v>
       </c>
       <c r="E110" t="n">
-        <v>-50.9</v>
+        <v>-92.37</v>
       </c>
       <c r="F110" t="n">
         <v>-90</v>
@@ -3848,27 +3848,27 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>JP1</t>
+          <t>L6</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>CAN Bus Term</t>
+          <t>BLM21PG121SN1D</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>PinHeader_1x02_P1.27mm_Vertical</t>
+          <t>L_0805_2012Metric</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>268</v>
+        <v>237.85</v>
       </c>
       <c r="E111" t="n">
-        <v>-55</v>
+        <v>-78.9375</v>
       </c>
       <c r="F111" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -3879,27 +3879,27 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>1uH 3.3A 40mΩ</t>
+          <t>BUK762R4-60E</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>L_1008_2520Metric</t>
+          <t>TO-263-2_L10.1-W9.1-P5.08-LS15.2-BR</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>216.825</v>
+        <v>264.75</v>
       </c>
       <c r="E112" t="n">
-        <v>-48.5</v>
+        <v>-88.43000000000001</v>
       </c>
       <c r="F112" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -3910,27 +3910,27 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>L5</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>CDRH104RNP-150NC</t>
+          <t>10K</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>IND-SMD_L10.2-W10.0</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>235.2</v>
+        <v>215.76</v>
       </c>
       <c r="E113" t="n">
-        <v>-92.37</v>
+        <v>-50.5</v>
       </c>
       <c r="F113" t="n">
-        <v>-90</v>
+        <v>180</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -3941,27 +3941,27 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>L6</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>BLM21PG121SN1D</t>
+          <t>100K</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>L_0805_2012Metric</t>
+          <t>R_0805_2012Metric</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>237.85</v>
+        <v>208.1625</v>
       </c>
       <c r="E114" t="n">
-        <v>-78.9375</v>
+        <v>-51.75</v>
       </c>
       <c r="F114" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -3972,27 +3972,27 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>BUK762R4-60E</t>
+          <t>22K</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>TO-263-2_L10.1-W9.1-P5.08-LS15.2-BR</t>
+          <t>R_0805_2012Metric</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>264.75</v>
+        <v>211.6625</v>
       </c>
       <c r="E115" t="n">
-        <v>-88.43000000000001</v>
+        <v>-51.75</v>
       </c>
       <c r="F115" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R10</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4017,13 +4017,13 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>215.76</v>
+        <v>229.01</v>
       </c>
       <c r="E116" t="n">
-        <v>-50.5</v>
+        <v>-87.375</v>
       </c>
       <c r="F116" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -4034,27 +4034,27 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>100K</t>
+          <t>3k24</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>R_0805_2012Metric</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>208.1625</v>
+        <v>227.01</v>
       </c>
       <c r="E117" t="n">
-        <v>-51.75</v>
+        <v>-87.375</v>
       </c>
       <c r="F117" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -4065,12 +4065,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>R8</t>
+          <t>R14</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>22K</t>
+          <t>120</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4079,13 +4079,13 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>211.6625</v>
+        <v>202.9875</v>
       </c>
       <c r="E118" t="n">
-        <v>-51.75</v>
+        <v>-59</v>
       </c>
       <c r="F118" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -4096,27 +4096,27 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>R10</t>
+          <t>R16</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>10K/1W</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>R_2512_6332Metric</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>229.01</v>
+        <v>205.325</v>
       </c>
       <c r="E119" t="n">
-        <v>-87.375</v>
+        <v>-62</v>
       </c>
       <c r="F119" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -4127,27 +4127,27 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R21</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>3k24</t>
+          <t>120</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>R_0805_2012Metric</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>227.01</v>
+        <v>263.9125</v>
       </c>
       <c r="E120" t="n">
-        <v>-87.375</v>
+        <v>-47.75</v>
       </c>
       <c r="F120" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -4158,27 +4158,27 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>R13</t>
+          <t>R22</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1K</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>R_0603_1608Metric</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>229.575</v>
+        <v>202.335</v>
       </c>
       <c r="E121" t="n">
-        <v>-86.125</v>
+        <v>-65.98</v>
       </c>
       <c r="F121" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>R14</t>
+          <t>R23</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4203,13 +4203,13 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>202.9875</v>
+        <v>207.9125</v>
       </c>
       <c r="E122" t="n">
-        <v>-59</v>
+        <v>-67.48</v>
       </c>
       <c r="F122" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -4220,24 +4220,24 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>R16</t>
+          <t>R26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>10K/1W</t>
+          <t>10K</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>R_2512_6332Metric</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>205.325</v>
+        <v>208.835</v>
       </c>
       <c r="E123" t="n">
-        <v>-62</v>
+        <v>-64.98</v>
       </c>
       <c r="F123" t="n">
         <v>180</v>
@@ -4251,27 +4251,27 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>R21</t>
+          <t>R29</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>1K</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>R_0805_2012Metric</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>263.9125</v>
+        <v>248.715</v>
       </c>
       <c r="E124" t="n">
-        <v>-47.75</v>
+        <v>-78.09</v>
       </c>
       <c r="F124" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -4282,27 +4282,27 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>R22</t>
+          <t>R31</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>1K</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>R_0805_2012Metric</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>202.335</v>
+        <v>257.1375</v>
       </c>
       <c r="E125" t="n">
-        <v>-65.98</v>
+        <v>-85.25</v>
       </c>
       <c r="F125" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -4313,24 +4313,24 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>R23</t>
+          <t>R32</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>10K</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>R_0805_2012Metric</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>207.9125</v>
+        <v>248.715</v>
       </c>
       <c r="E126" t="n">
-        <v>-67.48</v>
+        <v>-79.09</v>
       </c>
       <c r="F126" t="n">
         <v>180</v>
@@ -4344,12 +4344,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>R26</t>
+          <t>R33</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>470R</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4358,13 +4358,13 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>208.835</v>
+        <v>251.58</v>
       </c>
       <c r="E127" t="n">
-        <v>-64.98</v>
+        <v>-68.37</v>
       </c>
       <c r="F127" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -4375,24 +4375,24 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>R29</t>
+          <t>R34</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>1K</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>R0402</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>248.715</v>
+        <v>253.7</v>
       </c>
       <c r="E128" t="n">
-        <v>-78.09</v>
+        <v>-68.41</v>
       </c>
       <c r="F128" t="n">
         <v>0</v>
@@ -4406,24 +4406,24 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>R31</t>
+          <t>R40</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10K</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>R_0805_2012Metric</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>257.1375</v>
+        <v>264.74</v>
       </c>
       <c r="E129" t="n">
-        <v>-85.25</v>
+        <v>-81.75</v>
       </c>
       <c r="F129" t="n">
         <v>180</v>
@@ -4437,24 +4437,24 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>R32</t>
+          <t>R46</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>47K/1W</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>R_2512_6332Metric</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>248.715</v>
+        <v>213.7875</v>
       </c>
       <c r="E130" t="n">
-        <v>-79.09</v>
+        <v>-60.25</v>
       </c>
       <c r="F130" t="n">
         <v>180</v>
@@ -4468,12 +4468,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>R33</t>
+          <t>R48</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>470R</t>
+          <t>47K</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4482,13 +4482,13 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>251.58</v>
+        <v>230.075</v>
       </c>
       <c r="E131" t="n">
-        <v>-68.37</v>
+        <v>-58.5</v>
       </c>
       <c r="F131" t="n">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
@@ -4499,27 +4499,27 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>R34</t>
+          <t>R50</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>120</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>R0402</t>
+          <t>R_0805_2012Metric</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>253.7</v>
+        <v>251.6375</v>
       </c>
       <c r="E132" t="n">
-        <v>-68.41</v>
+        <v>-78.59</v>
       </c>
       <c r="F132" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -4530,27 +4530,27 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>R40</t>
+          <t>Relay1</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>SRD-12VDC-SL-C</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>RELAY-TH_SRD-XXVDC-XL-C</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>264.74</v>
+        <v>214.3</v>
       </c>
       <c r="E133" t="n">
-        <v>-81.75</v>
+        <v>-81.5</v>
       </c>
       <c r="F133" t="n">
-        <v>180</v>
+        <v>-90</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -4561,24 +4561,24 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>R46</t>
+          <t>Reset1</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>47K/1W</t>
+          <t>Reset</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>R_2512_6332Metric</t>
+          <t>SW_Push_1P1T_XKB_TS-1187A</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>213.7875</v>
+        <v>238.36</v>
       </c>
       <c r="E134" t="n">
-        <v>-60.25</v>
+        <v>-69.11499999999999</v>
       </c>
       <c r="F134" t="n">
         <v>180</v>
@@ -4592,27 +4592,27 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>R48</t>
+          <t>U1</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>47K</t>
+          <t>SY8089A1AAC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>TSOT-23-5</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>230.075</v>
+        <v>212.6375</v>
       </c>
       <c r="E135" t="n">
-        <v>-58.5</v>
+        <v>-48.8</v>
       </c>
       <c r="F135" t="n">
-        <v>-90</v>
+        <v>180</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -4623,27 +4623,27 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>R50</t>
+          <t>U2</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>INA226</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>R_0805_2012Metric</t>
+          <t>VSSOP-10_3x3mm_P0.5mm</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>251.6375</v>
+        <v>265.55</v>
       </c>
       <c r="E136" t="n">
-        <v>-78.59</v>
+        <v>-61.29</v>
       </c>
       <c r="F136" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -4654,27 +4654,27 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Relay1</t>
+          <t>U3</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>SRD-12VDC-SL-C</t>
+          <t>TPS5430DDA</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>RELAY-TH_SRD-XXVDC-XL-C</t>
+          <t>TI_SO-PowerPAD-8_ThermalVias</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>214.3</v>
+        <v>225.25</v>
       </c>
       <c r="E137" t="n">
-        <v>-81.5</v>
+        <v>-90.875</v>
       </c>
       <c r="F137" t="n">
-        <v>-90</v>
+        <v>180</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -4685,27 +4685,27 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Reset1</t>
+          <t>U4</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Reset</t>
+          <t>DB125-3.5-2P-GN-S</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>SW_Push_1P1T_XKB_TS-1187A</t>
+          <t>CONN-TH_2P-P3.50_L7.4-W7.0</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>238.36</v>
+        <v>273.75</v>
       </c>
       <c r="E138" t="n">
-        <v>-69.11499999999999</v>
+        <v>-60.77</v>
       </c>
       <c r="F138" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -4716,27 +4716,27 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>U1</t>
+          <t>U5</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>SY8089A1AAC</t>
+          <t>DB125-3.5-2P-GN-S</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>TSOT-23-5</t>
+          <t>CONN-TH_2P-P3.50_L7.4-W7.0</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>212.6375</v>
+        <v>274</v>
       </c>
       <c r="E139" t="n">
-        <v>-48.8</v>
+        <v>-68.77</v>
       </c>
       <c r="F139" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -4747,27 +4747,27 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>U2</t>
+          <t>U6</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>INA226</t>
+          <t>DB125-3.5-2P-GN-S</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>VSSOP-10_3x3mm_P0.5mm</t>
+          <t>CONN-TH_2P-P3.50_L7.4-W7.0</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>265.55</v>
+        <v>274</v>
       </c>
       <c r="E140" t="n">
-        <v>-61.29</v>
+        <v>-76.27</v>
       </c>
       <c r="F140" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -4778,27 +4778,27 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>U3</t>
+          <t>U7</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>TPS5430DDA</t>
+          <t>DB125-3.5-3P-GN-S</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>TI_SO-PowerPAD-8_ThermalVias</t>
+          <t>CONN-TH_3P-P3.50_L7.4-W10.5</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>225.25</v>
+        <v>273.25</v>
       </c>
       <c r="E141" t="n">
-        <v>-90.875</v>
+        <v>-51.25</v>
       </c>
       <c r="F141" t="n">
-        <v>180</v>
+        <v>-90</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -4809,27 +4809,27 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>U4</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>DB125-3.5-2P-GN-S</t>
+          <t>ESP32-S3-WROOM-2-N32R16V</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>CONN-TH_2P-P3.50_L7.4-W7.0</t>
+          <t>ESP32-S3-WROOM-2</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>273.75</v>
+        <v>244.61</v>
       </c>
       <c r="E142" t="n">
-        <v>-60.77</v>
+        <v>-50.91</v>
       </c>
       <c r="F142" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -4840,27 +4840,27 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>U5</t>
+          <t>U9</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>DB125-3.5-2P-GN-S</t>
+          <t>DB125-3.5-3P-GN-S</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>CONN-TH_2P-P3.50_L7.4-W7.0</t>
+          <t>CONN-TH_3P-P3.50_L7.4-W10.5</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>274</v>
+        <v>206.5</v>
       </c>
       <c r="E143" t="n">
-        <v>-68.77</v>
+        <v>-41.25</v>
       </c>
       <c r="F143" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -4871,27 +4871,27 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>U6</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>DB125-3.5-2P-GN-S</t>
+          <t>SN65HVD230DR</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>CONN-TH_2P-P3.50_L7.4-W7.0</t>
+          <t>SOIC-8_3.9x4.9mm_P1.27mm</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>274</v>
+        <v>262.275</v>
       </c>
       <c r="E144" t="n">
-        <v>-76.27</v>
+        <v>-51.825</v>
       </c>
       <c r="F144" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>U7</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4916,13 +4916,13 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>273.25</v>
+        <v>206.55</v>
       </c>
       <c r="E145" t="n">
-        <v>-51.25</v>
+        <v>-101.6</v>
       </c>
       <c r="F145" t="n">
-        <v>-90</v>
+        <v>180</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -4933,27 +4933,27 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U13</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>ESP32-S3-WROOM-2-N32R16V</t>
+          <t>DB125-3.5-3P-GN-S</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>ESP32-S3-WROOM-2</t>
+          <t>CONN-TH_3P-P3.50_L7.4-W10.5</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>244.61</v>
+        <v>197.325</v>
       </c>
       <c r="E146" t="n">
-        <v>-50.91</v>
+        <v>-63.25</v>
       </c>
       <c r="F146" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -4964,27 +4964,27 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>DB125-3.5-3P-GN-S</t>
+          <t>PC817C-S</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>CONN-TH_3P-P3.50_L7.4-W10.5</t>
+          <t>SOP-4_L6.5-W4.6-P2.54-LS10.3-TL</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>206.5</v>
+        <v>247.8</v>
       </c>
       <c r="E147" t="n">
-        <v>-41.25</v>
+        <v>-82.25</v>
       </c>
       <c r="F147" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -4995,24 +4995,24 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U18</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>SN65HVD230DR</t>
+          <t>INA226</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>SOIC-8_3.9x4.9mm_P1.27mm</t>
+          <t>VSSOP-10_3x3mm_P0.5mm</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>262.275</v>
+        <v>266.3</v>
       </c>
       <c r="E148" t="n">
-        <v>-51.825</v>
+        <v>-69.52</v>
       </c>
       <c r="F148" t="n">
         <v>0</v>
@@ -5026,27 +5026,27 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U19</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>DB125-3.5-3P-GN-S</t>
+          <t>INA226</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>CONN-TH_3P-P3.50_L7.4-W10.5</t>
+          <t>VSSOP-10_3x3mm_P0.5mm</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>206.55</v>
+        <v>267.25</v>
       </c>
       <c r="E149" t="n">
-        <v>-101.6</v>
+        <v>-75.52</v>
       </c>
       <c r="F149" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -5057,24 +5057,24 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>U13</t>
+          <t>U21</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>DB125-3.5-3P-GN-S</t>
+          <t>PC817C-S</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>CONN-TH_3P-P3.50_L7.4-W10.5</t>
+          <t>SOP-4_L6.5-W4.6-P2.54-LS10.3-TL</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>197.325</v>
+        <v>227.075</v>
       </c>
       <c r="E150" t="n">
-        <v>-63.25</v>
+        <v>-62.75</v>
       </c>
       <c r="F150" t="n">
         <v>90</v>
@@ -5088,153 +5088,29 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>PC817C-S</t>
+          <t>MCP1407-E/MF_C640313</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>SOP-4_L6.5-W4.6-P2.54-LS10.3-TL</t>
+          <t>DFN-8_L6.0-W5.0-P1.27-BL-EP4.0</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>247.8</v>
+        <v>257.865</v>
       </c>
       <c r="E151" t="n">
-        <v>-82.25</v>
+        <v>-80.3075</v>
       </c>
       <c r="F151" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G151" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>U18</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>INA226</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>VSSOP-10_3x3mm_P0.5mm</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>266.3</v>
-      </c>
-      <c r="E152" t="n">
-        <v>-69.52</v>
-      </c>
-      <c r="F152" t="n">
-        <v>0</v>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>U19</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>INA226</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>VSSOP-10_3x3mm_P0.5mm</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>267.25</v>
-      </c>
-      <c r="E153" t="n">
-        <v>-75.52</v>
-      </c>
-      <c r="F153" t="n">
-        <v>0</v>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>U21</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>PC817C-S</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>SOP-4_L6.5-W4.6-P2.54-LS10.3-TL</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>227.075</v>
-      </c>
-      <c r="E154" t="n">
-        <v>-62.75</v>
-      </c>
-      <c r="F154" t="n">
-        <v>90</v>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>U23</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>MCP1407-E/MF_C640313</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>DFN-8_L6.0-W5.0-P1.27-BL-EP4.0</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>257.865</v>
-      </c>
-      <c r="E155" t="n">
-        <v>-80.3075</v>
-      </c>
-      <c r="F155" t="n">
-        <v>0</v>
-      </c>
-      <c r="G155" t="inlineStr">
         <is>
           <t>Top</t>
         </is>

--- a/MarineBoard/production/MarineBoard-positions.xlsx
+++ b/MarineBoard/production/MarineBoard-positions.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G151"/>
+  <dimension ref="A1:G152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -593,12 +593,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C10</t>
+          <t>C11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4.7uF</t>
+          <t>0.1uF</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -607,13 +607,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>266.25</v>
+        <v>267.77</v>
       </c>
       <c r="E6" t="n">
-        <v>-60.79</v>
+        <v>-63.29</v>
       </c>
       <c r="F6" t="n">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C11</t>
+          <t>C12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -638,13 +638,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>267.77</v>
+        <v>265.25</v>
       </c>
       <c r="E7" t="n">
-        <v>-63.29</v>
+        <v>-60.81</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -655,24 +655,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C12</t>
+          <t>C13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.1uF</t>
+          <t>10uF/50V</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>C_0402_1005Metric</t>
+          <t>C_0805_2012Metric</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>265.25</v>
+        <v>216.25</v>
       </c>
       <c r="E8" t="n">
-        <v>-60.81</v>
+        <v>-96.825</v>
       </c>
       <c r="F8" t="n">
         <v>-90</v>
@@ -686,27 +686,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C13</t>
+          <t>C14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10uF/50V</t>
+          <t>0.1uF</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>C_0805_2012Metric</t>
+          <t>C_0402_1005Metric</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>216.25</v>
+        <v>218.48</v>
       </c>
       <c r="E9" t="n">
-        <v>-96.825</v>
+        <v>-97.125</v>
       </c>
       <c r="F9" t="n">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -717,27 +717,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C14</t>
+          <t>C15</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.1uF</t>
+          <t>47uF</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>C_0402_1005Metric</t>
+          <t>C_1206_3216Metric</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>218.48</v>
+        <v>226</v>
       </c>
       <c r="E10" t="n">
-        <v>-97.125</v>
+        <v>-85.90000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -748,24 +748,24 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C15</t>
+          <t>C19</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>47uF</t>
+          <t>0.1uF</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>C_1206_3216Metric</t>
+          <t>C_0402_1005Metric</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="E11" t="n">
-        <v>-85.90000000000001</v>
+        <v>-79.605</v>
       </c>
       <c r="F11" t="n">
         <v>90</v>
@@ -779,12 +779,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C19</t>
+          <t>C26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.1uF</t>
+          <t>47nF</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>240</v>
+        <v>263.25</v>
       </c>
       <c r="E12" t="n">
-        <v>-79.605</v>
+        <v>-50.595</v>
       </c>
       <c r="F12" t="n">
         <v>90</v>
@@ -810,12 +810,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C26</t>
+          <t>C27</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>47nF</t>
+          <t>0.1uF</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>263.25</v>
+        <v>266.5</v>
       </c>
       <c r="E13" t="n">
-        <v>-50.595</v>
+        <v>-55.27</v>
       </c>
       <c r="F13" t="n">
         <v>90</v>
@@ -841,7 +841,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C27</t>
+          <t>C28</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -855,13 +855,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>266.5</v>
+        <v>259.5</v>
       </c>
       <c r="E14" t="n">
-        <v>-55.27</v>
+        <v>-51.73</v>
       </c>
       <c r="F14" t="n">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -872,12 +872,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C28</t>
+          <t>C29</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0.1uF</t>
+          <t>47nF</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -886,10 +886,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>259.5</v>
+        <v>263.25</v>
       </c>
       <c r="E15" t="n">
-        <v>-51.73</v>
+        <v>-52.98</v>
       </c>
       <c r="F15" t="n">
         <v>-90</v>
@@ -903,12 +903,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C29</t>
+          <t>C30</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>47nF</t>
+          <t>4.7uF</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -917,10 +917,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>263.25</v>
+        <v>260.75</v>
       </c>
       <c r="E16" t="n">
-        <v>-52.98</v>
+        <v>-51.805</v>
       </c>
       <c r="F16" t="n">
         <v>-90</v>
@@ -934,12 +934,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C30</t>
+          <t>C31</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4.7uF</t>
+          <t>0.1uF</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>260.75</v>
+        <v>267.2</v>
       </c>
       <c r="E17" t="n">
-        <v>-51.805</v>
+        <v>-69.52</v>
       </c>
       <c r="F17" t="n">
         <v>-90</v>
@@ -965,7 +965,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C31</t>
+          <t>C32</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>267.2</v>
+        <v>268</v>
       </c>
       <c r="E18" t="n">
-        <v>-69.52</v>
+        <v>-75.75</v>
       </c>
       <c r="F18" t="n">
         <v>-90</v>
@@ -996,7 +996,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C32</t>
+          <t>C34</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1010,13 +1010,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>268</v>
+        <v>239.75</v>
       </c>
       <c r="E19" t="n">
-        <v>-75.75</v>
+        <v>-67.75</v>
       </c>
       <c r="F19" t="n">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C34</t>
+          <t>C35</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>239.75</v>
+        <v>247.75</v>
       </c>
       <c r="E20" t="n">
-        <v>-67.75</v>
+        <v>-67.77</v>
       </c>
       <c r="F20" t="n">
         <v>90</v>
@@ -1058,7 +1058,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C35</t>
+          <t>C37</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1072,13 +1072,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>247.75</v>
+        <v>271.52</v>
       </c>
       <c r="E21" t="n">
-        <v>-67.77</v>
+        <v>-74.02</v>
       </c>
       <c r="F21" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C37</t>
+          <t>C38</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1103,13 +1103,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>271.52</v>
+        <v>270.25</v>
       </c>
       <c r="E22" t="n">
-        <v>-74.02</v>
+        <v>-69.25</v>
       </c>
       <c r="F22" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1120,27 +1120,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C38</t>
+          <t>C39</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0.1uF</t>
+          <t>1.2uF 100V</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>C_0402_1005Metric</t>
+          <t>C_1210_3225Metric</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>270.25</v>
+        <v>200.8</v>
       </c>
       <c r="E23" t="n">
-        <v>-69.25</v>
+        <v>-62.5</v>
       </c>
       <c r="F23" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1151,27 +1151,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C39</t>
+          <t>C42</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1.2uF 100V</t>
+          <t>0.1uF</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>C_1210_3225Metric</t>
+          <t>C_0402_1005Metric</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>200.8</v>
+        <v>254.25</v>
       </c>
       <c r="E24" t="n">
-        <v>-62.5</v>
+        <v>-78.52</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1182,27 +1182,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>C42</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0.1uF</t>
+          <t>H5VL10B</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>C_0402_1005Metric</t>
+          <t>D_SOD-882</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>254.25</v>
+        <v>204.505</v>
       </c>
       <c r="E25" t="n">
-        <v>-78.52</v>
+        <v>-48.5</v>
       </c>
       <c r="F25" t="n">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1230,7 +1230,7 @@
         <v>204.505</v>
       </c>
       <c r="E26" t="n">
-        <v>-48.5</v>
+        <v>-53.25</v>
       </c>
       <c r="F26" t="n">
         <v>90</v>
@@ -1244,27 +1244,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H5VL10B</t>
+          <t>SMBJ18A</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>D_SOD-882</t>
+          <t>D_SMB</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>204.505</v>
+        <v>236.4</v>
       </c>
       <c r="E27" t="n">
-        <v>-53.25</v>
+        <v>-96.125</v>
       </c>
       <c r="F27" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1275,27 +1275,27 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>D6</t>
+          <t>D9</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SMBJ18A</t>
+          <t>ESD5Z3.3T1G</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>D_SMB</t>
+          <t>D_SOD-523</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>236.4</v>
+        <v>199.325</v>
       </c>
       <c r="E28" t="n">
-        <v>-96.125</v>
+        <v>-59.45</v>
       </c>
       <c r="F28" t="n">
-        <v>180</v>
+        <v>-90</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>D9</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>199.325</v>
+        <v>260.95</v>
       </c>
       <c r="E29" t="n">
-        <v>-59.45</v>
+        <v>-60.25</v>
       </c>
       <c r="F29" t="n">
         <v>-90</v>
@@ -1337,7 +1337,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>D11</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1351,13 +1351,13 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>260.95</v>
+        <v>258</v>
       </c>
       <c r="E30" t="n">
-        <v>-60.25</v>
+        <v>-62.45</v>
       </c>
       <c r="F30" t="n">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1368,27 +1368,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D14</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ESD5Z3.3T1G</t>
+          <t>SS56</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>D_SOD-523</t>
+          <t>D_SMA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>258</v>
+        <v>229</v>
       </c>
       <c r="E31" t="n">
-        <v>-62.45</v>
+        <v>-96.375</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1399,12 +1399,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>D14</t>
+          <t>D15</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SS56</t>
+          <t>SS14</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1413,13 +1413,13 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>229</v>
+        <v>212.57</v>
       </c>
       <c r="E32" t="n">
-        <v>-96.375</v>
+        <v>-87.55</v>
       </c>
       <c r="F32" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1430,24 +1430,24 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>D15</t>
+          <t>D18</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SS14</t>
+          <t>ESD5Z3.3T1G</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>D_SMA</t>
+          <t>D_SOD-523</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>212.57</v>
+        <v>271.5</v>
       </c>
       <c r="E33" t="n">
-        <v>-87.55</v>
+        <v>-69.47</v>
       </c>
       <c r="F33" t="n">
         <v>90</v>
@@ -1461,7 +1461,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>D18</t>
+          <t>D19</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1475,13 +1475,13 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>271.5</v>
+        <v>271.75</v>
       </c>
       <c r="E34" t="n">
-        <v>-69.47</v>
+        <v>-76.06999999999999</v>
       </c>
       <c r="F34" t="n">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1492,27 +1492,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>D19</t>
+          <t>D20</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ESD5Z3.3T1G</t>
+          <t>MBRS3100T3G</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>D_SOD-523</t>
+          <t>D_SMC</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>271.75</v>
+        <v>214.425</v>
       </c>
       <c r="E35" t="n">
-        <v>-76.06999999999999</v>
+        <v>-60.25</v>
       </c>
       <c r="F35" t="n">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1523,27 +1523,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>D20</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MBRS3100T3G</t>
+          <t>1N4148W</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>D_SMC</t>
+          <t>D_SOD-123</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>214.425</v>
+        <v>253.23</v>
       </c>
       <c r="E36" t="n">
-        <v>-60.25</v>
+        <v>-68.88</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -3538,27 +3538,27 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>D22</t>
+          <t>D17</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>S3MB-13-F</t>
+          <t>SS14</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>D_SMB</t>
+          <t>D_SMA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>221.825</v>
+        <v>258.7</v>
       </c>
       <c r="E101" t="n">
-        <v>-62</v>
+        <v>-73.52</v>
       </c>
       <c r="F101" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -3569,27 +3569,27 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2A</t>
+          <t>S3MB-13-F</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>FUSE-TH_XF-506P</t>
+          <t>D_SMB</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>233.25</v>
+        <v>221.825</v>
       </c>
       <c r="E102" t="n">
-        <v>-100.875</v>
+        <v>-62</v>
       </c>
       <c r="F102" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -3600,12 +3600,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>1A</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3614,13 +3614,13 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>229.07</v>
+        <v>233.25</v>
       </c>
       <c r="E103" t="n">
-        <v>-75.17</v>
+        <v>-100.875</v>
       </c>
       <c r="F103" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -3631,12 +3631,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>10A</t>
+          <t>1A</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3645,13 +3645,13 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>259.85</v>
+        <v>229.07</v>
       </c>
       <c r="E104" t="n">
-        <v>-101</v>
+        <v>-75.17</v>
       </c>
       <c r="F104" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F3</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3676,13 +3676,13 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>205.95</v>
+        <v>259.85</v>
       </c>
       <c r="E105" t="n">
-        <v>-75.5</v>
+        <v>-101</v>
       </c>
       <c r="F105" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -3693,24 +3693,24 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Flash1</t>
+          <t>F4</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Flash</t>
+          <t>10A</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>SW_Push_1P1T_XKB_TS-1187A</t>
+          <t>FUSE-TH_XF-506P</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>246.5</v>
+        <v>205.95</v>
       </c>
       <c r="E106" t="n">
-        <v>-69.11499999999999</v>
+        <v>-75.5</v>
       </c>
       <c r="F106" t="n">
         <v>180</v>
@@ -3724,27 +3724,27 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>J1</t>
+          <t>Flash1</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>USB_C_Receptacle_USB2.0_16P</t>
+          <t>Flash</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>USB_C_Receptacle_HCTL_HC-TYPE-C-16P-01A</t>
+          <t>SW_Push_1P1T_XKB_TS-1187A</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>198.755</v>
+        <v>246.5</v>
       </c>
       <c r="E107" t="n">
-        <v>-50.9</v>
+        <v>-69.11499999999999</v>
       </c>
       <c r="F107" t="n">
-        <v>-90</v>
+        <v>180</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -3755,27 +3755,27 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>JP1</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>CAN Bus Term</t>
+          <t>USB_C_Receptacle_USB2.0_16P</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>PinHeader_1x02_P1.27mm_Vertical</t>
+          <t>USB_C_Receptacle_HCTL_HC-TYPE-C-16P-01A</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>268</v>
+        <v>198.755</v>
       </c>
       <c r="E108" t="n">
-        <v>-55</v>
+        <v>-50.9</v>
       </c>
       <c r="F108" t="n">
-        <v>180</v>
+        <v>-90</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -3786,27 +3786,27 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>JP1</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>1uH 3.3A 40mΩ</t>
+          <t>CAN Bus Term</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>L_1008_2520Metric</t>
+          <t>PinHeader_1x02_P1.27mm_Vertical</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>216.825</v>
+        <v>268</v>
       </c>
       <c r="E109" t="n">
-        <v>-48.5</v>
+        <v>-55</v>
       </c>
       <c r="F109" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -3817,27 +3817,27 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>L5</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>CDRH104RNP-150NC</t>
+          <t>1uH 3.3A 40mΩ</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>IND-SMD_L10.2-W10.0</t>
+          <t>L_1008_2520Metric</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>235.2</v>
+        <v>216.825</v>
       </c>
       <c r="E110" t="n">
-        <v>-92.37</v>
+        <v>-48.5</v>
       </c>
       <c r="F110" t="n">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -3848,27 +3848,27 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>L6</t>
+          <t>L5</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>BLM21PG121SN1D</t>
+          <t>CDRH104RNP-150NC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>L_0805_2012Metric</t>
+          <t>IND-SMD_L10.2-W10.0</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>237.85</v>
+        <v>235.2</v>
       </c>
       <c r="E111" t="n">
-        <v>-78.9375</v>
+        <v>-92.37</v>
       </c>
       <c r="F111" t="n">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -3879,24 +3879,24 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>L6</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>BUK762R4-60E</t>
+          <t>BLM21PG121SN1D</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>TO-263-2_L10.1-W9.1-P5.08-LS15.2-BR</t>
+          <t>L_0805_2012Metric</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>264.75</v>
+        <v>237.85</v>
       </c>
       <c r="E112" t="n">
-        <v>-88.43000000000001</v>
+        <v>-78.9375</v>
       </c>
       <c r="F112" t="n">
         <v>90</v>
@@ -3910,27 +3910,27 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>BUK762R4-60E</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>TO-263-2_L10.1-W9.1-P5.08-LS15.2-BR</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>215.76</v>
+        <v>264.75</v>
       </c>
       <c r="E113" t="n">
-        <v>-50.5</v>
+        <v>-88.43000000000001</v>
       </c>
       <c r="F113" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -3941,24 +3941,24 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>100K</t>
+          <t>10K</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>R_0805_2012Metric</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>208.1625</v>
+        <v>215.76</v>
       </c>
       <c r="E114" t="n">
-        <v>-51.75</v>
+        <v>-50.5</v>
       </c>
       <c r="F114" t="n">
         <v>180</v>
@@ -3972,12 +3972,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>R8</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>22K</t>
+          <t>100K</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3986,7 +3986,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>211.6625</v>
+        <v>208.1625</v>
       </c>
       <c r="E115" t="n">
         <v>-51.75</v>
@@ -4003,27 +4003,27 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>R10</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>22K</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>R_0805_2012Metric</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>229.01</v>
+        <v>211.6625</v>
       </c>
       <c r="E116" t="n">
-        <v>-87.375</v>
+        <v>-51.75</v>
       </c>
       <c r="F116" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -4034,12 +4034,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R10</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>3k24</t>
+          <t>10K</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>227.01</v>
+        <v>229.01</v>
       </c>
       <c r="E117" t="n">
         <v>-87.375</v>
@@ -4065,24 +4065,24 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>R14</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>3k24</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>R_0805_2012Metric</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>202.9875</v>
+        <v>227.01</v>
       </c>
       <c r="E118" t="n">
-        <v>-59</v>
+        <v>-87.375</v>
       </c>
       <c r="F118" t="n">
         <v>0</v>
@@ -4096,27 +4096,27 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>R16</t>
+          <t>R14</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>10K/1W</t>
+          <t>120</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>R_2512_6332Metric</t>
+          <t>R_0805_2012Metric</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>205.325</v>
+        <v>202.9875</v>
       </c>
       <c r="E119" t="n">
-        <v>-62</v>
+        <v>-59</v>
       </c>
       <c r="F119" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -4127,24 +4127,24 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>R21</t>
+          <t>R16</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>10K/1W</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>R_0805_2012Metric</t>
+          <t>R_2512_6332Metric</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>263.9125</v>
+        <v>205.325</v>
       </c>
       <c r="E120" t="n">
-        <v>-47.75</v>
+        <v>-62</v>
       </c>
       <c r="F120" t="n">
         <v>180</v>
@@ -4158,27 +4158,27 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>R22</t>
+          <t>R21</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>1K</t>
+          <t>120</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>R_0805_2012Metric</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>202.335</v>
+        <v>263.9125</v>
       </c>
       <c r="E121" t="n">
-        <v>-65.98</v>
+        <v>-47.75</v>
       </c>
       <c r="F121" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -4189,27 +4189,27 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>R23</t>
+          <t>R22</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>1K</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>R_0805_2012Metric</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>207.9125</v>
+        <v>202.335</v>
       </c>
       <c r="E122" t="n">
-        <v>-67.48</v>
+        <v>-65.98</v>
       </c>
       <c r="F122" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -4220,24 +4220,24 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>R26</t>
+          <t>R23</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>120</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>R_0805_2012Metric</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>208.835</v>
+        <v>207.9125</v>
       </c>
       <c r="E123" t="n">
-        <v>-64.98</v>
+        <v>-67.48</v>
       </c>
       <c r="F123" t="n">
         <v>180</v>
@@ -4251,12 +4251,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>R29</t>
+          <t>R26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>1K</t>
+          <t>10K</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4265,13 +4265,13 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>248.715</v>
+        <v>208.835</v>
       </c>
       <c r="E124" t="n">
-        <v>-78.09</v>
+        <v>-64.98</v>
       </c>
       <c r="F124" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -4282,27 +4282,27 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>R31</t>
+          <t>R29</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1K</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>R_0805_2012Metric</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>257.1375</v>
+        <v>248.715</v>
       </c>
       <c r="E125" t="n">
-        <v>-85.25</v>
+        <v>-78.09</v>
       </c>
       <c r="F125" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -4313,24 +4313,24 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>R32</t>
+          <t>R31</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>R_0805_2012Metric</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>248.715</v>
+        <v>257.1375</v>
       </c>
       <c r="E126" t="n">
-        <v>-79.09</v>
+        <v>-85.25</v>
       </c>
       <c r="F126" t="n">
         <v>180</v>
@@ -4344,12 +4344,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>R33</t>
+          <t>R32</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>470R</t>
+          <t>10K</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4358,13 +4358,13 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>251.58</v>
+        <v>248.715</v>
       </c>
       <c r="E127" t="n">
-        <v>-68.37</v>
+        <v>-79.09</v>
       </c>
       <c r="F127" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -4375,24 +4375,24 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>R34</t>
+          <t>R33</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>470R</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>R0402</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>253.7</v>
+        <v>251.58</v>
       </c>
       <c r="E128" t="n">
-        <v>-68.41</v>
+        <v>-68.37</v>
       </c>
       <c r="F128" t="n">
         <v>0</v>
@@ -4406,27 +4406,27 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>R40</t>
+          <t>R34</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>10K</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>R0402</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>264.74</v>
+        <v>253.7</v>
       </c>
       <c r="E129" t="n">
-        <v>-81.75</v>
+        <v>-68.41</v>
       </c>
       <c r="F129" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -4437,24 +4437,24 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>R46</t>
+          <t>R40</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>47K/1W</t>
+          <t>10K</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>R_2512_6332Metric</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>213.7875</v>
+        <v>264.74</v>
       </c>
       <c r="E130" t="n">
-        <v>-60.25</v>
+        <v>-81.75</v>
       </c>
       <c r="F130" t="n">
         <v>180</v>
@@ -4468,27 +4468,27 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>R48</t>
+          <t>R46</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>47K</t>
+          <t>47K/1W</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>R_2512_6332Metric</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>230.075</v>
+        <v>213.7875</v>
       </c>
       <c r="E131" t="n">
-        <v>-58.5</v>
+        <v>-60.25</v>
       </c>
       <c r="F131" t="n">
-        <v>-90</v>
+        <v>180</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
@@ -4499,27 +4499,27 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>R50</t>
+          <t>R48</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>47K</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>R_0805_2012Metric</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>251.6375</v>
+        <v>230.075</v>
       </c>
       <c r="E132" t="n">
-        <v>-78.59</v>
+        <v>-58.5</v>
       </c>
       <c r="F132" t="n">
-        <v>180</v>
+        <v>-90</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -4530,27 +4530,27 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Relay1</t>
+          <t>R50</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>SRD-12VDC-SL-C</t>
+          <t>120</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>RELAY-TH_SRD-XXVDC-XL-C</t>
+          <t>R_0805_2012Metric</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>214.3</v>
+        <v>251.6375</v>
       </c>
       <c r="E133" t="n">
-        <v>-81.5</v>
+        <v>-78.59</v>
       </c>
       <c r="F133" t="n">
-        <v>-90</v>
+        <v>180</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -4561,27 +4561,27 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Reset1</t>
+          <t>Relay1</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Reset</t>
+          <t>SRD-12VDC-SL-C</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>SW_Push_1P1T_XKB_TS-1187A</t>
+          <t>RELAY-TH_SRD-XXVDC-XL-C</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>238.36</v>
+        <v>214.3</v>
       </c>
       <c r="E134" t="n">
-        <v>-69.11499999999999</v>
+        <v>-81.5</v>
       </c>
       <c r="F134" t="n">
-        <v>180</v>
+        <v>-90</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -4592,24 +4592,24 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>U1</t>
+          <t>Reset1</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>SY8089A1AAC</t>
+          <t>Reset</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>TSOT-23-5</t>
+          <t>SW_Push_1P1T_XKB_TS-1187A</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>212.6375</v>
+        <v>238.36</v>
       </c>
       <c r="E135" t="n">
-        <v>-48.8</v>
+        <v>-69.11499999999999</v>
       </c>
       <c r="F135" t="n">
         <v>180</v>
@@ -4623,27 +4623,27 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>U2</t>
+          <t>U1</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>INA226</t>
+          <t>SY8089A1AAC</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>VSSOP-10_3x3mm_P0.5mm</t>
+          <t>TSOT-23-5</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>265.55</v>
+        <v>212.6375</v>
       </c>
       <c r="E136" t="n">
-        <v>-61.29</v>
+        <v>-48.8</v>
       </c>
       <c r="F136" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -4654,27 +4654,27 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>U3</t>
+          <t>U2</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>TPS5430DDA</t>
+          <t>INA226</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>TI_SO-PowerPAD-8_ThermalVias</t>
+          <t>VSSOP-10_3x3mm_P0.5mm</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>225.25</v>
+        <v>265.55</v>
       </c>
       <c r="E137" t="n">
-        <v>-90.875</v>
+        <v>-61.29</v>
       </c>
       <c r="F137" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -4685,27 +4685,27 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>U4</t>
+          <t>U3</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>DB125-3.5-2P-GN-S</t>
+          <t>TPS5430DDA</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>CONN-TH_2P-P3.50_L7.4-W7.0</t>
+          <t>TI_SO-PowerPAD-8_ThermalVias</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>273.75</v>
+        <v>225.25</v>
       </c>
       <c r="E138" t="n">
-        <v>-60.77</v>
+        <v>-90.875</v>
       </c>
       <c r="F138" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>U5</t>
+          <t>U4</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4730,10 +4730,10 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>274</v>
+        <v>273.75</v>
       </c>
       <c r="E139" t="n">
-        <v>-68.77</v>
+        <v>-60.77</v>
       </c>
       <c r="F139" t="n">
         <v>90</v>
@@ -4747,7 +4747,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>U6</t>
+          <t>U5</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4764,7 +4764,7 @@
         <v>274</v>
       </c>
       <c r="E140" t="n">
-        <v>-76.27</v>
+        <v>-68.77</v>
       </c>
       <c r="F140" t="n">
         <v>90</v>
@@ -4778,27 +4778,27 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>U7</t>
+          <t>U6</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>DB125-3.5-3P-GN-S</t>
+          <t>DB125-3.5-2P-GN-S</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>CONN-TH_3P-P3.50_L7.4-W10.5</t>
+          <t>CONN-TH_2P-P3.50_L7.4-W7.0</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>273.25</v>
+        <v>274</v>
       </c>
       <c r="E141" t="n">
-        <v>-51.25</v>
+        <v>-76.27</v>
       </c>
       <c r="F141" t="n">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -4809,27 +4809,27 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U7</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>ESP32-S3-WROOM-2-N32R16V</t>
+          <t>DB125-3.5-3P-GN-S</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>ESP32-S3-WROOM-2</t>
+          <t>CONN-TH_3P-P3.50_L7.4-W10.5</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>244.61</v>
+        <v>273.25</v>
       </c>
       <c r="E142" t="n">
-        <v>-50.91</v>
+        <v>-51.25</v>
       </c>
       <c r="F142" t="n">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -4840,24 +4840,24 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U8</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>DB125-3.5-3P-GN-S</t>
+          <t>ESP32-S3-WROOM-2-N32R16V</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>CONN-TH_3P-P3.50_L7.4-W10.5</t>
+          <t>ESP32-S3-WROOM-2</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>206.5</v>
+        <v>244.61</v>
       </c>
       <c r="E143" t="n">
-        <v>-41.25</v>
+        <v>-50.91</v>
       </c>
       <c r="F143" t="n">
         <v>0</v>
@@ -4871,24 +4871,24 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U9</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>SN65HVD230DR</t>
+          <t>DB125-3.5-3P-GN-S</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>SOIC-8_3.9x4.9mm_P1.27mm</t>
+          <t>CONN-TH_3P-P3.50_L7.4-W10.5</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>262.275</v>
+        <v>206.5</v>
       </c>
       <c r="E144" t="n">
-        <v>-51.825</v>
+        <v>-41.25</v>
       </c>
       <c r="F144" t="n">
         <v>0</v>
@@ -4902,27 +4902,27 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>DB125-3.5-3P-GN-S</t>
+          <t>SN65HVD230DR</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>CONN-TH_3P-P3.50_L7.4-W10.5</t>
+          <t>SOIC-8_3.9x4.9mm_P1.27mm</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>206.55</v>
+        <v>262.275</v>
       </c>
       <c r="E145" t="n">
-        <v>-101.6</v>
+        <v>-51.825</v>
       </c>
       <c r="F145" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>U13</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4947,13 +4947,13 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>197.325</v>
+        <v>206.55</v>
       </c>
       <c r="E146" t="n">
-        <v>-63.25</v>
+        <v>-101.6</v>
       </c>
       <c r="F146" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -4964,27 +4964,27 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>U13</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>PC817C-S</t>
+          <t>DB125-3.5-3P-GN-S</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>SOP-4_L6.5-W4.6-P2.54-LS10.3-TL</t>
+          <t>CONN-TH_3P-P3.50_L7.4-W10.5</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>247.8</v>
+        <v>197.325</v>
       </c>
       <c r="E147" t="n">
-        <v>-82.25</v>
+        <v>-63.25</v>
       </c>
       <c r="F147" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -4995,27 +4995,27 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>U18</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>INA226</t>
+          <t>PC817C-S</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>VSSOP-10_3x3mm_P0.5mm</t>
+          <t>SOP-4_L6.5-W4.6-P2.54-LS10.3-TL</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>266.3</v>
+        <v>247.8</v>
       </c>
       <c r="E148" t="n">
-        <v>-69.52</v>
+        <v>-82.25</v>
       </c>
       <c r="F148" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>U19</t>
+          <t>U18</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -5040,10 +5040,10 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>267.25</v>
+        <v>266.3</v>
       </c>
       <c r="E149" t="n">
-        <v>-75.52</v>
+        <v>-69.52</v>
       </c>
       <c r="F149" t="n">
         <v>0</v>
@@ -5057,27 +5057,27 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>U21</t>
+          <t>U19</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>PC817C-S</t>
+          <t>INA226</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>SOP-4_L6.5-W4.6-P2.54-LS10.3-TL</t>
+          <t>VSSOP-10_3x3mm_P0.5mm</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>227.075</v>
+        <v>267.25</v>
       </c>
       <c r="E150" t="n">
-        <v>-62.75</v>
+        <v>-75.52</v>
       </c>
       <c r="F150" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
@@ -5088,29 +5088,60 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
+          <t>U21</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>PC817C-S</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>SOP-4_L6.5-W4.6-P2.54-LS10.3-TL</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>227.075</v>
+      </c>
+      <c r="E151" t="n">
+        <v>-62.75</v>
+      </c>
+      <c r="F151" t="n">
+        <v>90</v>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Top</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
           <t>U23</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr">
+      <c r="B152" t="inlineStr">
         <is>
           <t>MCP1407-E/MF_C640313</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr">
+      <c r="C152" t="inlineStr">
         <is>
           <t>DFN-8_L6.0-W5.0-P1.27-BL-EP4.0</t>
         </is>
       </c>
-      <c r="D151" t="n">
+      <c r="D152" t="n">
         <v>257.865</v>
       </c>
-      <c r="E151" t="n">
+      <c r="E152" t="n">
         <v>-80.3075</v>
       </c>
-      <c r="F151" t="n">
+      <c r="F152" t="n">
         <v>0</v>
       </c>
-      <c r="G151" t="inlineStr">
+      <c r="G152" t="inlineStr">
         <is>
           <t>Top</t>
         </is>

--- a/MarineBoard/production/MarineBoard-positions.xlsx
+++ b/MarineBoard/production/MarineBoard-positions.xlsx
@@ -1652,7 +1652,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FerriteBead</t>
+          <t>BLM21PG331SN1D</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>FerriteBead</t>
+          <t>BLM21PG331SN1D</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>FerriteBead</t>
+          <t>BLM21PG331SN1D</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>LED</t>
+          <t>KT-0603R</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>MCP1407-E/MF_C640313</t>
+          <t>MCP1407-E/MF</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
